--- a/planning/소반_세팅_시안.xlsx
+++ b/planning/소반_세팅_시안.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,17 +45,13 @@
     </font>
     <font>
       <name val="Pretendard"/>
-      <color rgb="00C00000"/>
-    </font>
-    <font>
-      <name val="Pretendard"/>
       <color rgb="00444444"/>
     </font>
     <font>
       <name val="Pretendard"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -65,11 +61,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EEEEEE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -97,11 +88,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -482,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소반 4상 세팅 시안 (2026-10-07) — 파란 글씨는 시안 값, 언제든 고쳐 쓰세요</t>
+          <t>소반 4상 세팅 시안 (2026-10-07 수정) — 파란 글씨는 시안 값, 언제든 고쳐 쓰세요</t>
         </is>
       </c>
     </row>
@@ -796,24 +784,24 @@
           <t>원산지(뒷벽 표시판용)</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>자료 없음</t>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>에티오피아(2종)</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>콜롬비아 라 에스메랄다(게이샤) + 콜롬비아 엘 포르베니르(카투라)</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>자료 없음</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>자료 없음</t>
+          <t>콜롬비아(라 에스메랄다 게이샤 + 엘 포르베니르 카투라)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>브라질 + 인도</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>에티오피아 + 브라질</t>
         </is>
       </c>
     </row>
@@ -879,28 +867,28 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>· 실물을 쓰고, 시들거나 상태가 나빠 보이면 바로 버리고 새로 올리기</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>· 확인 시각: 문 열기 전(9:30) · 점심(13:00) · 오후(15:30)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>· "향만 맡아 주세요" 작은 표시를 반찬그릇 옆에</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>· 분쇄 원두는 산화가 빨라 매일 아침 새로 갈아 담기</t>
         </is>
@@ -963,393 +951,393 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>인쇄</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>뒷벽 원산지 표시판</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>식당 원산지 표시처럼 4종 원산지·볶은 곳</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>발주·구매 3번과 같은 품목, 내용만 확정</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>인쇄</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>소반 스탠딩 안내판</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>4 + 여분 1</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>소반마다 커피 설명</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>A5 세움 거치대 필요</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>인쇄</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>수저 봉투 차림표</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>1,000</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>손님께 드림. 앞면 4종 메뉴</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>4일 최대 약 900명(추정) + 여분</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>인쇄</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>쿠폰 카드(봉투 속)</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>1,000</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>쇼핑몰 10% 할인 QR</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>수저 대신 넣음</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>인쇄</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>원두 김장 계산 카드</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>2~3</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>판매대 디스플레이</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>"하루 2잔이면 한 달 약 900g"</t>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>확정(10/7): "하루 1잔이면 한 달 약 450g, 겨울 석 달이면 약 1.35kg" (1잔 15g 기준)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>인쇄</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>원두 주문 QR 카드</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>아임웹 현장 주문(무료배송) 안내</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>판매대</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>인쇄</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>B2B 상담 예약 QR 카드</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>상담 예약 폼 안내</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>명함함 옆</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>인쇄</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>B2B 안내 브로셔</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>자료 없음</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>사장님께 드림</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>발주·구매 9번</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>소품</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>명함함</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>사장님 명함 받기</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr"/>
+      <c r="E12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>소품</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>넘김식 숫자판(3자리)</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>오늘 대접한 손님 ***명</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>숫자 높이 10cm 이상 추천, 발주·구매 18번</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>소품</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>그릇 세트(밥·국·반찬2)</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>4세트 + 여분</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>소반 세팅</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>사기 그릇 진열용</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>소품</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>작은 은 주전자</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>4 + 여분 2</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>시음 커피</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>소품</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>연출용 수저·수저 봉투</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>4세트</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>소반 연출</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr"/>
+      <c r="E16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>소모품</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>향미 원물</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>매일</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>반찬그릇 ②</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>말린 꽃·생허브·죠리퐁·보리·블루베리·초콜릿</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>복장</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>앞치마(광목 / 발표자 쪽빛)</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>인원수</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>전원 광목, 발표자 쪽빛</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>복장 확정 필요</t>
         </is>

--- a/planning/소반_세팅_시안.xlsx
+++ b/planning/소반_세팅_시안.xlsx
@@ -481,6 +481,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -548,7 +549,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>허벌 블렌드</t>
+          <t>허벌 블랜드</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -764,7 +765,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>향긋한 나물처럼, 허브향이 짙은 카페쇼 한정 블렌드.</t>
+          <t>향긋한 나물처럼, 허브향이 짙은 카페쇼 한정 블랜드.</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -859,6 +860,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
@@ -923,6 +925,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>

--- a/planning/소반_세팅_시안.xlsx
+++ b/planning/소반_세팅_시안.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>향긋한 나물처럼, 허브향이 짙은 카페쇼 한정 블랜드.</t>
+          <t>향긋한 나물처럼, 허브향이 짙은 이번 시즌 블랜드.</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
